--- a/data/trans_dic/P57_AC_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,94; 63,02</t>
+          <t>54,39; 63,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,01; 61,83</t>
+          <t>52,53; 61,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,51; 78,85</t>
+          <t>70,06; 79,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,11; 52,36</t>
+          <t>33,87; 52,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,59; 65,31</t>
+          <t>56,31; 65,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,58; 66,79</t>
+          <t>57,17; 66,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,38; 78,64</t>
+          <t>70,15; 78,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,22; 52,24</t>
+          <t>37,24; 53,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,76; 63,11</t>
+          <t>56,67; 63,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56,26; 63,33</t>
+          <t>56,32; 62,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,57; 78,12</t>
+          <t>71,35; 77,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,91; 50,24</t>
+          <t>37,92; 50,11</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,17; 66,99</t>
+          <t>59,23; 66,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,09; 66,31</t>
+          <t>58,59; 66,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,58; 80,73</t>
+          <t>73,36; 80,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,53; 64,91</t>
+          <t>52,55; 64,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,94; 69,78</t>
+          <t>62,26; 69,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,71; 73,37</t>
+          <t>65,74; 73,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,79; 81,75</t>
+          <t>74,8; 81,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,17; 56,44</t>
+          <t>29,05; 56,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,86; 66,99</t>
+          <t>61,83; 67,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63,46; 68,84</t>
+          <t>63,54; 68,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,32; 80,08</t>
+          <t>75,09; 79,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,9; 58,16</t>
+          <t>41,15; 57,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,04; 72,25</t>
+          <t>65,21; 72,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,71; 71,83</t>
+          <t>64,78; 72,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,49; 81,25</t>
+          <t>74,46; 81,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,81; 65,11</t>
+          <t>56,26; 65,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,36; 73,17</t>
+          <t>66,02; 73,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,09; 78,02</t>
+          <t>70,7; 77,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,23; 82,48</t>
+          <t>76,32; 82,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,51; 63,4</t>
+          <t>56,31; 63,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 72,22</t>
+          <t>66,89; 71,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,89; 73,98</t>
+          <t>69,1; 74,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,47; 81,02</t>
+          <t>76,52; 81,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,48; 63,06</t>
+          <t>57,57; 63,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,58; 74,75</t>
+          <t>66,48; 75,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,92; 72,97</t>
+          <t>64,35; 72,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,61; 84,23</t>
+          <t>77,31; 83,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,84; 62,75</t>
+          <t>21,2; 62,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,9; 73,93</t>
+          <t>65,8; 73,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,73; 81,68</t>
+          <t>74,87; 81,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,86; 86,62</t>
+          <t>80,61; 86,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,33; 64,92</t>
+          <t>50,21; 64,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,53; 73,25</t>
+          <t>67,33; 73,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,94; 76,33</t>
+          <t>70,72; 76,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,18; 84,56</t>
+          <t>80,03; 84,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,95; 62,33</t>
+          <t>32,58; 62,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,46; 75,02</t>
+          <t>65,34; 74,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,91; 68,86</t>
+          <t>59,12; 68,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,51; 84,69</t>
+          <t>77,39; 84,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,25; 71,62</t>
+          <t>63,73; 71,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 80,6</t>
+          <t>72,38; 81,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,17; 77,5</t>
+          <t>69,18; 77,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,37; 87,24</t>
+          <t>80,0; 86,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,22; 74,13</t>
+          <t>68,38; 74,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,13; 76,5</t>
+          <t>70,49; 76,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,63; 71,96</t>
+          <t>65,71; 71,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,86; 85,14</t>
+          <t>79,88; 85,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,28; 71,88</t>
+          <t>67,44; 72,08</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,86; 81,92</t>
+          <t>72,57; 81,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67,67; 77,78</t>
+          <t>68,26; 78,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,5; 82,86</t>
+          <t>73,37; 82,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61,73; 70,03</t>
+          <t>61,95; 69,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,47; 81,84</t>
+          <t>72,92; 81,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,69; 80,64</t>
+          <t>71,65; 80,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,88; 91,73</t>
+          <t>85,03; 91,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62,25; 68,7</t>
+          <t>62,25; 68,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74,18; 80,46</t>
+          <t>74,07; 80,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71,85; 78,36</t>
+          <t>71,55; 78,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80,84; 86,48</t>
+          <t>80,88; 86,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,27; 68,25</t>
+          <t>63,24; 68,55</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,44; 84,16</t>
+          <t>73,24; 84,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,49; 80,9</t>
+          <t>69,18; 80,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,11; 88,45</t>
+          <t>79,89; 88,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66,14; 75,1</t>
+          <t>66,81; 75,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,46; 85,22</t>
+          <t>76,74; 85,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,51; 81,52</t>
+          <t>72,64; 81,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,55; 90,98</t>
+          <t>83,2; 90,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,49; 77,49</t>
+          <t>71,63; 77,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76,85; 83,85</t>
+          <t>76,8; 83,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,63; 79,97</t>
+          <t>72,7; 79,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82,92; 88,83</t>
+          <t>83,25; 88,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,44; 75,73</t>
+          <t>70,57; 75,42</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>66,31; 69,51</t>
+          <t>66,37; 69,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,6; 68,03</t>
+          <t>64,68; 67,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,55; 80,41</t>
+          <t>77,61; 80,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42,97; 61,91</t>
+          <t>43,84; 61,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,09; 72,13</t>
+          <t>69,12; 72,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,68; 74,62</t>
+          <t>71,8; 74,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,87; 83,32</t>
+          <t>80,77; 83,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,56; 63,26</t>
+          <t>56,74; 63,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,49</t>
+          <t>68,26; 70,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68,72; 70,99</t>
+          <t>68,67; 70,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79,66; 81,6</t>
+          <t>79,7; 81,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,74; 61,7</t>
+          <t>51,79; 61,75</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>266503; 311345</t>
+          <t>268719; 311459</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>234164; 278348</t>
+          <t>236501; 277932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>295745; 330742</t>
+          <t>293889; 332504</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138951; 207197</t>
+          <t>134056; 205969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>264533; 305329</t>
+          <t>263252; 305037</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>246594; 286019</t>
+          <t>244825; 285884</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>277874; 310456</t>
+          <t>276946; 311015</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113557; 159390</t>
+          <t>113622; 162329</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>545814; 606811</t>
+          <t>544915; 606464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>494194; 556353</t>
+          <t>494762; 551435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>582773; 636056</t>
+          <t>580969; 633418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>265726; 352148</t>
+          <t>265750; 351240</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>435211; 492701</t>
+          <t>435611; 491134</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>403365; 452665</t>
+          <t>399950; 454749</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>427742; 469324</t>
+          <t>426459; 468271</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>221755; 274018</t>
+          <t>221857; 273316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>386704; 435691</t>
+          <t>388733; 435546</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>400972; 447723</t>
+          <t>401195; 448352</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>418965; 457941</t>
+          <t>419011; 457773</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>158498; 287021</t>
+          <t>147736; 285323</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>841209; 910884</t>
+          <t>840774; 914430</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>820501; 889996</t>
+          <t>821465; 889522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>859832; 914118</t>
+          <t>857224; 913028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>362036; 541285</t>
+          <t>382952; 539609</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>414701; 460666</t>
+          <t>415776; 461706</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>438779; 487000</t>
+          <t>439258; 489462</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497797; 542923</t>
+          <t>497596; 541386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>297076; 346588</t>
+          <t>299488; 346863</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>457084; 503974</t>
+          <t>454739; 504406</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>502425; 551388</t>
+          <t>499663; 548017</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>501235; 542352</t>
+          <t>501862; 544211</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>305613; 342872</t>
+          <t>304540; 342544</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>888810; 957866</t>
+          <t>887169; 953850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>953962; 1024451</t>
+          <t>956902; 1027499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1013872; 1074085</t>
+          <t>1014520; 1076416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>616798; 676756</t>
+          <t>617852; 678000</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>344614; 386910</t>
+          <t>344104; 388364</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396344; 445498</t>
+          <t>392848; 441206</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>498024; 540498</t>
+          <t>496128; 537701</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174584; 552264</t>
+          <t>186558; 554414</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>339804; 381228</t>
+          <t>339312; 379782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>459773; 502530</t>
+          <t>460624; 503014</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>520187; 557248</t>
+          <t>518549; 558336</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>361183; 456808</t>
+          <t>353312; 457199</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>697793; 756839</t>
+          <t>695679; 754729</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>869557; 935643</t>
+          <t>866784; 935001</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1030349; 1086559</t>
+          <t>1028440; 1084222</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>490177; 987132</t>
+          <t>515930; 988998</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>253138; 290116</t>
+          <t>252684; 288827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>250475; 292784</t>
+          <t>251355; 292916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>369531; 403803</t>
+          <t>368989; 405059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>358974; 400135</t>
+          <t>356032; 400491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>292690; 325620</t>
+          <t>292424; 327295</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>309041; 346219</t>
+          <t>309079; 346172</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>395677; 429498</t>
+          <t>393831; 427357</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>368740; 400670</t>
+          <t>369610; 400874</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>554535; 604884</t>
+          <t>557386; 605140</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>572251; 627447</t>
+          <t>572970; 627093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>773894; 825083</t>
+          <t>774085; 824915</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>739583; 790063</t>
+          <t>741296; 792280</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>210256; 239696</t>
+          <t>212330; 238442</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>207597; 238618</t>
+          <t>209430; 241531</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244938; 276163</t>
+          <t>244530; 274981</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>224667; 254895</t>
+          <t>225463; 254021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>251959; 280653</t>
+          <t>250076; 279882</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>249801; 280972</t>
+          <t>249671; 282010</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>318022; 343680</t>
+          <t>318584; 342712</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>244551; 269876</t>
+          <t>244550; 270655</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>471449; 511309</t>
+          <t>470703; 511791</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>470783; 513427</t>
+          <t>468842; 513876</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>572338; 612259</t>
+          <t>572586; 611477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>478816; 516527</t>
+          <t>478590; 518778</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154143; 176646</t>
+          <t>153728; 177287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>170685; 198715</t>
+          <t>169926; 198200</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>205185; 226554</t>
+          <t>204614; 225997</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>182191; 206898</t>
+          <t>184059; 207725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>255312; 284557</t>
+          <t>256244; 285383</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>277383; 311829</t>
+          <t>277863; 311774</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>333297; 362936</t>
+          <t>331871; 362483</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>297688; 322653</t>
+          <t>298255; 323313</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417917; 455984</t>
+          <t>417623; 456612</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>456196; 502307</t>
+          <t>456684; 500285</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>543133; 581871</t>
+          <t>545296; 580973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>487360; 523984</t>
+          <t>488255; 521794</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2170969; 2275537</t>
+          <t>2172811; 2281084</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2195742; 2312300</t>
+          <t>2198487; 2310203</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2618813; 2715505</t>
+          <t>2620694; 2717371</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1473323; 2122379</t>
+          <t>1502962; 2115993</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2333250; 2435811</t>
+          <t>2334164; 2444053</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2536064; 2640140</t>
+          <t>2540611; 2644727</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2847958; 2934358</t>
+          <t>2844493; 2937690</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1927645; 2155887</t>
+          <t>1933782; 2152435</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4539778; 4688116</t>
+          <t>4540249; 4681898</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4767294; 4924822</t>
+          <t>4763531; 4918237</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5495187; 5628988</t>
+          <t>5497943; 5625830</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3468951; 4218069</t>
+          <t>3540564; 4221190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AC_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,39; 63,04</t>
+          <t>54,64; 63,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,53; 61,73</t>
+          <t>52,51; 61,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,06; 79,27</t>
+          <t>71,05; 79,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,87; 52,05</t>
+          <t>37,48; 53,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,31; 65,25</t>
+          <t>56,59; 65,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,17; 66,75</t>
+          <t>57,82; 66,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,15; 78,78</t>
+          <t>70,7; 79,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,24; 53,2</t>
+          <t>40,5; 55,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,67; 63,07</t>
+          <t>56,86; 62,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56,32; 62,77</t>
+          <t>56,41; 62,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71,35; 77,79</t>
+          <t>71,88; 77,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,92; 50,11</t>
+          <t>40,94; 51,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,23; 66,78</t>
+          <t>59,63; 66,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,59; 66,62</t>
+          <t>58,98; 66,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,36; 80,55</t>
+          <t>73,49; 80,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,55; 64,74</t>
+          <t>54,61; 66,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,26; 69,76</t>
+          <t>62,01; 69,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,74; 73,47</t>
+          <t>65,67; 73,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,8; 81,72</t>
+          <t>75,02; 81,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 56,11</t>
+          <t>51,37; 60,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,83; 67,25</t>
+          <t>61,73; 67,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63,54; 68,8</t>
+          <t>63,49; 68,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,09; 79,98</t>
+          <t>75,12; 80,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,15; 57,98</t>
+          <t>54,68; 62,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,21; 72,41</t>
+          <t>64,61; 72,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,78; 72,19</t>
+          <t>64,88; 72,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,46; 81,02</t>
+          <t>74,7; 81,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,26; 65,16</t>
+          <t>58,68; 66,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,02; 73,23</t>
+          <t>66,67; 73,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,7; 77,54</t>
+          <t>70,92; 77,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,32; 82,76</t>
+          <t>76,53; 82,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,31; 63,33</t>
+          <t>58,57; 65,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,89; 71,92</t>
+          <t>66,86; 72,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,1; 74,2</t>
+          <t>69,3; 73,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,52; 81,19</t>
+          <t>76,51; 81,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,57; 63,18</t>
+          <t>59,62; 65,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,48; 75,03</t>
+          <t>66,46; 74,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,35; 72,27</t>
+          <t>64,61; 72,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,31; 83,79</t>
+          <t>77,51; 84,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,2; 62,99</t>
+          <t>57,89; 65,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,8; 73,65</t>
+          <t>65,47; 74,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,87; 81,76</t>
+          <t>75,01; 81,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,61; 86,79</t>
+          <t>80,73; 86,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,21; 64,98</t>
+          <t>61,48; 67,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,33; 73,04</t>
+          <t>67,39; 73,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,28</t>
+          <t>70,5; 75,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,03; 84,37</t>
+          <t>80,04; 84,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,58; 62,45</t>
+          <t>60,74; 65,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,34; 74,69</t>
+          <t>65,68; 75,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,12; 68,89</t>
+          <t>59,16; 69,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,39; 84,96</t>
+          <t>77,38; 84,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,73; 71,68</t>
+          <t>64,87; 72,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,38; 81,02</t>
+          <t>72,03; 80,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,18; 77,48</t>
+          <t>68,83; 77,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,0; 86,81</t>
+          <t>80,11; 87,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,38; 74,16</t>
+          <t>68,95; 74,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,49; 76,53</t>
+          <t>70,48; 76,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,71; 71,92</t>
+          <t>65,29; 71,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,88; 85,12</t>
+          <t>80,07; 85,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,44; 72,08</t>
+          <t>67,76; 72,33</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,57; 81,5</t>
+          <t>72,82; 82,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68,26; 78,73</t>
+          <t>68,32; 78,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,37; 82,51</t>
+          <t>73,01; 82,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61,95; 69,79</t>
+          <t>62,37; 70,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72,92; 81,61</t>
+          <t>73,07; 81,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,65; 80,93</t>
+          <t>71,93; 80,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,03; 91,47</t>
+          <t>85,22; 91,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62,25; 68,9</t>
+          <t>62,88; 69,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74,07; 80,53</t>
+          <t>73,95; 80,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71,55; 78,42</t>
+          <t>71,63; 78,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80,88; 86,37</t>
+          <t>80,99; 86,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,24; 68,55</t>
+          <t>63,61; 68,72</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,24; 84,47</t>
+          <t>73,18; 84,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,18; 80,69</t>
+          <t>69,51; 80,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,89; 88,23</t>
+          <t>79,98; 88,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66,81; 75,4</t>
+          <t>66,59; 75,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,74; 85,47</t>
+          <t>77,02; 85,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,64; 81,5</t>
+          <t>72,14; 81,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,2; 90,87</t>
+          <t>82,8; 90,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,63; 77,64</t>
+          <t>71,09; 77,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76,8; 83,97</t>
+          <t>77,58; 84,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,7; 79,64</t>
+          <t>72,73; 79,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83,25; 88,69</t>
+          <t>83,44; 88,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,57; 75,42</t>
+          <t>70,77; 75,82</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>66,37; 69,67</t>
+          <t>66,57; 69,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,68; 67,97</t>
+          <t>64,64; 67,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,61; 80,47</t>
+          <t>77,74; 80,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43,84; 61,72</t>
+          <t>60,61; 64,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,12; 72,37</t>
+          <t>69,18; 72,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,8; 74,75</t>
+          <t>71,74; 74,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,77; 83,42</t>
+          <t>80,88; 83,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,74; 63,16</t>
+          <t>62,44; 65,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,39</t>
+          <t>68,15; 70,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68,67; 70,9</t>
+          <t>68,75; 70,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79,7; 81,55</t>
+          <t>79,62; 81,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,79; 61,75</t>
+          <t>62,04; 64,4</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171835</t>
+          <t>184144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>136065</t>
+          <t>169050</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>307900</t>
+          <t>353195</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>268719; 311459</t>
+          <t>269933; 311775</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>236501; 277932</t>
+          <t>236392; 276819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>293889; 332504</t>
+          <t>298022; 332351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134056; 205969</t>
+          <t>151165; 217517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>263252; 305037</t>
+          <t>264530; 305970</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>244825; 285884</t>
+          <t>247606; 284860</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>276946; 311015</t>
+          <t>279134; 311915</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113622; 162329</t>
+          <t>143614; 195626</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>544915; 606464</t>
+          <t>546766; 602719</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>494762; 551435</t>
+          <t>495585; 552133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>580969; 633418</t>
+          <t>585268; 632109</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>265750; 351240</t>
+          <t>310265; 391955</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248854</t>
+          <t>287662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>239065</t>
+          <t>278875</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>487919</t>
+          <t>566537</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>435611; 491134</t>
+          <t>438558; 491056</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399950; 454749</t>
+          <t>402616; 454059</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>426459; 468271</t>
+          <t>427256; 469793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>221857; 273316</t>
+          <t>259606; 316836</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>388733; 435546</t>
+          <t>387170; 434706</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>401195; 448352</t>
+          <t>400784; 447251</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>419011; 457773</t>
+          <t>420258; 456258</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>147736; 285323</t>
+          <t>254969; 302332</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>840774; 914430</t>
+          <t>839473; 912490</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>821465; 889522</t>
+          <t>820896; 886763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>857224; 913028</t>
+          <t>857570; 913673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>382952; 539609</t>
+          <t>531318; 607595</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322647</t>
+          <t>384481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>324041</t>
+          <t>382851</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>646687</t>
+          <t>767333</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>415776; 461706</t>
+          <t>411932; 461309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>439258; 489462</t>
+          <t>439881; 490891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497596; 541386</t>
+          <t>499162; 541712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299488; 346863</t>
+          <t>360344; 409597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>454739; 504406</t>
+          <t>459171; 506588</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>499663; 548017</t>
+          <t>501233; 550166</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>501862; 544211</t>
+          <t>503253; 543979</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>304540; 342544</t>
+          <t>363028; 404368</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>887169; 953850</t>
+          <t>886765; 955291</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>956902; 1027499</t>
+          <t>959668; 1024636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1014520; 1076416</t>
+          <t>1014310; 1074712</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>617852; 678000</t>
+          <t>735687; 803018</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>388934</t>
+          <t>427958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>428491</t>
+          <t>468337</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>817425</t>
+          <t>896294</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>344104; 388364</t>
+          <t>343990; 387239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>392848; 441206</t>
+          <t>394441; 441808</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>496128; 537701</t>
+          <t>497401; 539092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>186558; 554414</t>
+          <t>400308; 455730</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>339312; 379782</t>
+          <t>337594; 382003</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>460624; 503014</t>
+          <t>461465; 502746</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>518549; 558336</t>
+          <t>519315; 555601</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>353312; 457199</t>
+          <t>447181; 488416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>695679; 754729</t>
+          <t>696287; 756863</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>866784; 935001</t>
+          <t>864128; 930488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1028440; 1084222</t>
+          <t>1028470; 1084103</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>515930; 988998</t>
+          <t>861784; 929043</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379593</t>
+          <t>416267</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>385679</t>
+          <t>431082</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>765272</t>
+          <t>847350</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>252684; 288827</t>
+          <t>253982; 291354</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>251355; 292916</t>
+          <t>251538; 294085</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368989; 405059</t>
+          <t>368953; 403538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>356032; 400491</t>
+          <t>393556; 437463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>292424; 327295</t>
+          <t>290979; 324714</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>309079; 346172</t>
+          <t>307507; 347465</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>393831; 427357</t>
+          <t>394385; 428439</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>369610; 400874</t>
+          <t>413877; 448052</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>557386; 605140</t>
+          <t>557275; 606323</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>572970; 627093</t>
+          <t>569305; 626556</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>774085; 824915</t>
+          <t>775959; 824141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>741296; 792280</t>
+          <t>817845; 872988</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241177</t>
+          <t>267684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>257679</t>
+          <t>283330</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>498856</t>
+          <t>551014</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212330; 238442</t>
+          <t>213050; 240356</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209430; 241531</t>
+          <t>209601; 241389</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>244530; 274981</t>
+          <t>243333; 275303</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>225463; 254021</t>
+          <t>251268; 282252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>250076; 279882</t>
+          <t>250594; 280109</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>249671; 282010</t>
+          <t>250636; 280943</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>318584; 342712</t>
+          <t>319307; 343338</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>244550; 270655</t>
+          <t>269944; 297885</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>470703; 511791</t>
+          <t>469945; 511096</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>468842; 513876</t>
+          <t>469344; 514459</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>572586; 611477</t>
+          <t>573400; 611774</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>478590; 518778</t>
+          <t>529318; 571908</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195576</t>
+          <t>215448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>310208</t>
+          <t>338410</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>505783</t>
+          <t>553858</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>153728; 177287</t>
+          <t>153595; 177141</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>169926; 198200</t>
+          <t>170744; 198067</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204614; 225997</t>
+          <t>204861; 225660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>184059; 207725</t>
+          <t>201427; 228237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>256244; 285383</t>
+          <t>257179; 286461</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>277863; 311774</t>
+          <t>275949; 309999</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>331871; 362483</t>
+          <t>330300; 361281</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>298255; 323313</t>
+          <t>323126; 351876</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417623; 456612</t>
+          <t>421880; 456971</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>456684; 500285</t>
+          <t>456833; 501067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>545296; 580973</t>
+          <t>546556; 581890</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>488255; 521794</t>
+          <t>535767; 573938</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1948615</t>
+          <t>2183645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2081228</t>
+          <t>2351934</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4029843</t>
+          <t>4535579</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2172811; 2281084</t>
+          <t>2179290; 2280419</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2198487; 2310203</t>
+          <t>2197132; 2310843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2620694; 2717371</t>
+          <t>2625373; 2718147</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1502962; 2115993</t>
+          <t>2119131; 2243836</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2334164; 2444053</t>
+          <t>2336294; 2438619</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2540611; 2644727</t>
+          <t>2538399; 2645490</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2844493; 2937690</t>
+          <t>2848419; 2940170</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1933782; 2152435</t>
+          <t>2299379; 2411260</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4540249; 4681898</t>
+          <t>4532346; 4684354</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4763531; 4918237</t>
+          <t>4769576; 4920842</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5497943; 5625830</t>
+          <t>5492814; 5627169</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3540564; 4221190</t>
+          <t>4453342; 4622930</t>
         </is>
       </c>
     </row>
